--- a/data/extracted/inventory-receipts/REP CONTENEDOR PIQUE TURQ 26.XLSX
+++ b/data/extracted/inventory-receipts/REP CONTENEDOR PIQUE TURQ 26.XLSX
@@ -1,18 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AF0036-DESKTOP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\txpacifico\txp-inventory\data\extracted\inventory-receipts\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED38387-3816-4E75-A1AA-535507A19D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="9465"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="IBUM" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -404,7 +406,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###,###,###,###,##0.#0"/>
   </numFmts>
@@ -445,12 +447,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -730,50 +731,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L64"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="12" width="10.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="12" width="10.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -811,12 +812,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -854,7 +855,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -892,7 +893,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -930,7 +931,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -968,7 +969,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -1006,7 +1007,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -1044,7 +1045,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -1082,7 +1083,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -1120,7 +1121,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -1158,7 +1159,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -1196,7 +1197,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -1234,7 +1235,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -1272,7 +1273,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -1310,7 +1311,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -1348,7 +1349,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -1386,7 +1387,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -1424,7 +1425,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
@@ -1462,7 +1463,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1500,7 +1501,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1538,7 +1539,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
@@ -1576,7 +1577,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
@@ -1614,7 +1615,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>19</v>
       </c>
@@ -1652,7 +1653,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
@@ -1690,7 +1691,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>19</v>
       </c>
@@ -1728,7 +1729,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>19</v>
       </c>
@@ -1766,7 +1767,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>19</v>
       </c>
@@ -1804,7 +1805,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>19</v>
       </c>
@@ -1842,7 +1843,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>19</v>
       </c>
@@ -1880,7 +1881,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>19</v>
       </c>
@@ -1918,7 +1919,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>19</v>
       </c>
@@ -1956,7 +1957,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>19</v>
       </c>
@@ -1994,7 +1995,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>19</v>
       </c>
@@ -2032,7 +2033,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>19</v>
       </c>
@@ -2070,7 +2071,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -2108,7 +2109,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>19</v>
       </c>
@@ -2146,7 +2147,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>19</v>
       </c>
@@ -2184,7 +2185,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>19</v>
       </c>
@@ -2222,7 +2223,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>19</v>
       </c>
@@ -2260,7 +2261,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>19</v>
       </c>
@@ -2298,7 +2299,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>19</v>
       </c>
@@ -2336,7 +2337,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>19</v>
       </c>
@@ -2374,7 +2375,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>19</v>
       </c>
@@ -2412,7 +2413,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>19</v>
       </c>
@@ -2450,7 +2451,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>19</v>
       </c>
@@ -2488,7 +2489,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F51" s="1" t="s">
         <v>113</v>
       </c>
@@ -2508,7 +2509,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F52" s="1" t="s">
         <v>115</v>
       </c>
@@ -2528,7 +2529,7 @@
         <v>762.9</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F53" s="1" t="s">
         <v>113</v>
       </c>
@@ -2548,7 +2549,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F54" s="1" t="s">
         <v>115</v>
       </c>
@@ -2568,7 +2569,7 @@
         <v>762.9</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F55" s="1" t="s">
         <v>113</v>
       </c>
@@ -2588,7 +2589,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F56" s="1" t="s">
         <v>115</v>
       </c>
@@ -2608,7 +2609,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F57" s="1" t="s">
         <v>113</v>
       </c>
@@ -2628,7 +2629,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>117</v>
       </c>
@@ -2663,7 +2664,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F60" s="1" t="s">
         <v>113</v>
       </c>
@@ -2683,12 +2684,12 @@
         <v>114</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K61" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>121</v>
       </c>
@@ -2723,7 +2724,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F63" s="1" t="s">
         <v>113</v>
       </c>
@@ -2743,7 +2744,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K64" s="2" t="s">
         <v>26</v>
       </c>
@@ -2752,4 +2753,19 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CDE4A70-A742-49FA-A23A-85212C604910}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>47328</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>